--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UNIVERSIDAD DEUSTO LOIOLA INDAUTXU.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UNIVERSIDAD DEUSTO LOIOLA INDAUTXU.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. LOPEZ BRETON</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>33.1433</v>
+        <v>37.6276</v>
       </c>
       <c r="E2" t="n">
-        <v>39.189</v>
+        <v>32.4633</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.045500000000001</v>
+        <v>5.1643</v>
       </c>
       <c r="G2" t="n">
-        <v>28.0708</v>
+        <v>46.7168</v>
       </c>
       <c r="H2" t="n">
-        <v>15.0901</v>
+        <v>25.2378</v>
       </c>
       <c r="I2" t="n">
-        <v>12.9808</v>
+        <v>21.4787</v>
       </c>
       <c r="J2" t="n">
-        <v>33.5963</v>
+        <v>65.6481</v>
       </c>
       <c r="K2" t="n">
-        <v>22.4869</v>
+        <v>37.5246</v>
       </c>
       <c r="L2" t="n">
-        <v>11.1099</v>
+        <v>28.1234</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.5254</v>
+        <v>-18.9314</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.3964</v>
+        <v>-12.2867</v>
       </c>
       <c r="O2" t="n">
-        <v>1.8712</v>
+        <v>-6.6447</v>
       </c>
       <c r="P2" t="n">
-        <v>-9.4574</v>
+        <v>-11.1944</v>
       </c>
       <c r="Q2" t="n">
-        <v>-42.2686</v>
+        <v>-54.428</v>
       </c>
       <c r="R2" t="n">
-        <v>32.8114</v>
+        <v>43.2338</v>
       </c>
       <c r="S2" t="n">
-        <v>21.3865</v>
+        <v>-3.304199999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>20.1025</v>
+        <v>-0.8077000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2838</v>
+        <v>-2.4961</v>
       </c>
       <c r="V2" t="n">
-        <v>-6.8566</v>
+        <v>5.4092</v>
       </c>
       <c r="W2" t="n">
-        <v>27.7588</v>
+        <v>22.0513</v>
       </c>
       <c r="X2" t="n">
-        <v>-34.6153</v>
+        <v>-16.642</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>A. LOPEZ BRETON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>22.3004</v>
+        <v>21.683</v>
       </c>
       <c r="E3" t="n">
-        <v>22.808</v>
+        <v>27.141</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5075999999999999</v>
+        <v>-5.4583</v>
       </c>
       <c r="G3" t="n">
-        <v>46.7168</v>
+        <v>28.0708</v>
       </c>
       <c r="H3" t="n">
-        <v>25.2378</v>
+        <v>15.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>21.4787</v>
+        <v>12.9808</v>
       </c>
       <c r="J3" t="n">
-        <v>65.6481</v>
+        <v>33.5963</v>
       </c>
       <c r="K3" t="n">
-        <v>37.5246</v>
+        <v>22.4869</v>
       </c>
       <c r="L3" t="n">
-        <v>28.1234</v>
+        <v>11.1099</v>
       </c>
       <c r="M3" t="n">
-        <v>-18.9314</v>
+        <v>-5.5254</v>
       </c>
       <c r="N3" t="n">
-        <v>-12.2867</v>
+        <v>-7.3964</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.6447</v>
+        <v>1.8712</v>
       </c>
       <c r="P3" t="n">
-        <v>-11.1944</v>
+        <v>-9.4574</v>
       </c>
       <c r="Q3" t="n">
-        <v>-54.428</v>
+        <v>-42.2686</v>
       </c>
       <c r="R3" t="n">
-        <v>43.2338</v>
+        <v>32.8114</v>
       </c>
       <c r="S3" t="n">
-        <v>-18.6312</v>
+        <v>9.9261</v>
       </c>
       <c r="T3" t="n">
-        <v>-10.4628</v>
+        <v>8.055199999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.168699999999999</v>
+        <v>1.8709</v>
       </c>
       <c r="V3" t="n">
-        <v>5.4092</v>
+        <v>-6.8566</v>
       </c>
       <c r="W3" t="n">
-        <v>22.0513</v>
+        <v>27.7588</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.642</v>
+        <v>-34.6153</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>17.4339</v>
+        <v>4.970999999999998</v>
       </c>
       <c r="E4" t="n">
-        <v>7.6774</v>
+        <v>1.6699</v>
       </c>
       <c r="F4" t="n">
-        <v>9.756499999999999</v>
+        <v>3.301</v>
       </c>
       <c r="G4" t="n">
         <v>25.3739</v>
@@ -766,13 +766,13 @@
         <v>50.9542</v>
       </c>
       <c r="S4" t="n">
-        <v>18.3944</v>
+        <v>5.9315</v>
       </c>
       <c r="T4" t="n">
-        <v>5.9763</v>
+        <v>-0.03119999999999989</v>
       </c>
       <c r="U4" t="n">
-        <v>12.4182</v>
+        <v>5.962999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-19.1929</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. AZKOAGA BENDEJACQ</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1834</v>
+        <v>2.2494</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.478000000000001</v>
+        <v>-16.8645</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6617</v>
+        <v>19.1133</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4045999999999996</v>
+        <v>-9.877699999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0618</v>
+        <v>1.5538</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4658</v>
+        <v>-11.432</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7563000000000003</v>
+        <v>-3.3938</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6110999999999996</v>
+        <v>10.1522</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3674</v>
+        <v>-13.546</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3515999999999999</v>
+        <v>-6.4842</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4504</v>
+        <v>-8.5982</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0985</v>
+        <v>2.114</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7019</v>
+        <v>7.7202</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.3691</v>
+        <v>-20.0726</v>
       </c>
       <c r="R5" t="n">
-        <v>9.071</v>
+        <v>27.7932</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.587</v>
+        <v>2.1458</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.5077</v>
+        <v>-1.2948</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07930000000000006</v>
+        <v>3.4406</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6642000000000001</v>
+        <v>2.2611</v>
       </c>
       <c r="W5" t="n">
-        <v>5.6428</v>
+        <v>7.8975</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.9786</v>
+        <v>-5.6364</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
+          <t>A. AZKOAGA BENDEJACQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6176999999999997</v>
+        <v>2.1808</v>
       </c>
       <c r="E6" t="n">
-        <v>18.8628</v>
+        <v>-1.7206</v>
       </c>
       <c r="F6" t="n">
-        <v>-19.4807</v>
+        <v>3.9016</v>
       </c>
       <c r="G6" t="n">
-        <v>16.0801</v>
+        <v>0.4045999999999996</v>
       </c>
       <c r="H6" t="n">
-        <v>11.9809</v>
+        <v>-2.0618</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0991</v>
+        <v>2.4658</v>
       </c>
       <c r="J6" t="n">
-        <v>37.4309</v>
+        <v>0.7563000000000003</v>
       </c>
       <c r="K6" t="n">
-        <v>24.1935</v>
+        <v>-0.6110999999999996</v>
       </c>
       <c r="L6" t="n">
-        <v>13.2377</v>
+        <v>1.3674</v>
       </c>
       <c r="M6" t="n">
-        <v>-21.3509</v>
+        <v>-0.3515999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-12.2126</v>
+        <v>-1.4504</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.138399999999999</v>
+        <v>1.0985</v>
       </c>
       <c r="P6" t="n">
-        <v>-16.0197</v>
+        <v>2.7019</v>
       </c>
       <c r="Q6" t="n">
-        <v>-51.5329</v>
+        <v>-6.3691</v>
       </c>
       <c r="R6" t="n">
-        <v>35.5134</v>
+        <v>9.071</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8889</v>
+        <v>-1.5898</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8317</v>
+        <v>-1.7502</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0574000000000002</v>
+        <v>0.1603999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.567299999999999</v>
+        <v>0.6642000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>29.1337</v>
+        <v>5.6428</v>
       </c>
       <c r="X6" t="n">
-        <v>-33.7008</v>
+        <v>-4.9786</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.278300000000001</v>
+        <v>-1.063300000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.5324</v>
+        <v>-5.0129</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2544</v>
+        <v>3.9496</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6865</v>
@@ -1000,13 +1000,13 @@
         <v>4.824999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5268</v>
+        <v>-0.3119</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.702</v>
+        <v>-0.1826</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8249000000000001</v>
+        <v>-0.1297</v>
       </c>
       <c r="V7" t="n">
         <v>0.1631</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2467</v>
+        <v>-3.516999999999997</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.4584</v>
+        <v>16.983</v>
       </c>
       <c r="F8" t="n">
-        <v>20.2119</v>
+        <v>-20.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.877699999999999</v>
+        <v>16.0801</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5538</v>
+        <v>11.9809</v>
       </c>
       <c r="I8" t="n">
-        <v>-11.432</v>
+        <v>4.0991</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.3938</v>
+        <v>37.4309</v>
       </c>
       <c r="K8" t="n">
-        <v>10.1522</v>
+        <v>24.1935</v>
       </c>
       <c r="L8" t="n">
-        <v>-13.546</v>
+        <v>13.2377</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.4842</v>
+        <v>-21.3509</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.5982</v>
+        <v>-12.2126</v>
       </c>
       <c r="O8" t="n">
-        <v>2.114</v>
+        <v>-9.138399999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>7.7202</v>
+        <v>-16.0197</v>
       </c>
       <c r="Q8" t="n">
-        <v>-20.0726</v>
+        <v>-51.5329</v>
       </c>
       <c r="R8" t="n">
-        <v>27.7932</v>
+        <v>35.5134</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.3499</v>
+        <v>0.9901999999999996</v>
       </c>
       <c r="T8" t="n">
-        <v>-7.8889</v>
+        <v>1.9518</v>
       </c>
       <c r="U8" t="n">
-        <v>4.5389</v>
+        <v>-0.962</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2611</v>
+        <v>-4.567299999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>7.8975</v>
+        <v>29.1337</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.6364</v>
+        <v>-33.7008</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. DIEZ TIDALA</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.4762</v>
+        <v>-5.3098</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.805400000000001</v>
+        <v>0.06960000000000122</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.6707</v>
+        <v>-5.379499999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.150499999999999</v>
+        <v>-6.7532</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0325</v>
+        <v>-3.687</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1183</v>
+        <v>-3.0659</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3284</v>
+        <v>14.4218</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.04689999999999994</v>
+        <v>9.2918</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3753</v>
+        <v>5.1301</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.4789</v>
+        <v>-21.1746</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.9856</v>
+        <v>-12.9791</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4935</v>
+        <v>-8.1959</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1929999999999999</v>
+        <v>9.264199999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.053</v>
+        <v>-27.2139</v>
       </c>
       <c r="R9" t="n">
-        <v>3.86</v>
+        <v>36.4786</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6187</v>
+        <v>-3.7852</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08079999999999987</v>
+        <v>-2.4355</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5382</v>
+        <v>-1.3495</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5139</v>
+        <v>-4.035900000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>15.2976</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5139</v>
+        <v>-19.3336</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>L. DIEZ TIDALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.35</v>
+        <v>-7.1296</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6634000000000002</v>
+        <v>-3.1277</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.6867</v>
+        <v>-4.0021</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.7532</v>
+        <v>-4.150499999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.687</v>
+        <v>-3.0325</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0659</v>
+        <v>-1.1183</v>
       </c>
       <c r="J10" t="n">
-        <v>14.4218</v>
+        <v>1.3284</v>
       </c>
       <c r="K10" t="n">
-        <v>9.2918</v>
+        <v>-0.04689999999999994</v>
       </c>
       <c r="L10" t="n">
-        <v>5.1301</v>
+        <v>1.3753</v>
       </c>
       <c r="M10" t="n">
-        <v>-21.1746</v>
+        <v>-5.4789</v>
       </c>
       <c r="N10" t="n">
-        <v>-12.9791</v>
+        <v>-2.9856</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.1959</v>
+        <v>-2.4935</v>
       </c>
       <c r="P10" t="n">
-        <v>9.264199999999999</v>
+        <v>-0.1929999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-27.2139</v>
+        <v>-4.053</v>
       </c>
       <c r="R10" t="n">
-        <v>36.4786</v>
+        <v>3.86</v>
       </c>
       <c r="S10" t="n">
-        <v>-8.8256</v>
+        <v>-1.2725</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.1684</v>
+        <v>-0.4028999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.6571</v>
+        <v>-0.8697</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.035900000000001</v>
+        <v>-1.5139</v>
       </c>
       <c r="W10" t="n">
-        <v>15.2976</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-19.3336</v>
+        <v>-1.5139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>P. MOLINA MATA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>-20.8311</v>
+        <v>-15.2922</v>
       </c>
       <c r="E11" t="n">
-        <v>-21.4569</v>
+        <v>-19.6017</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6256000000000002</v>
+        <v>4.3098</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.0098</v>
+        <v>-10.4457</v>
       </c>
       <c r="H11" t="n">
-        <v>7.0125</v>
+        <v>-7.9079</v>
       </c>
       <c r="I11" t="n">
-        <v>-13.0225</v>
+        <v>-2.5376</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0138999999999998</v>
+        <v>2.206799999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>9.5466</v>
+        <v>1.4584</v>
       </c>
       <c r="L11" t="n">
-        <v>-9.5603</v>
+        <v>0.7488000000000006</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.995699999999999</v>
+        <v>-12.6524</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.5339</v>
+        <v>-9.366199999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.4621</v>
+        <v>-3.2861</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5793000000000001</v>
+        <v>16.9846</v>
       </c>
       <c r="Q11" t="n">
-        <v>-20.6515</v>
+        <v>-19.6865</v>
       </c>
       <c r="R11" t="n">
-        <v>20.0723</v>
+        <v>36.6713</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.932300000000001</v>
+        <v>-2.2573</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.8342</v>
+        <v>-2.5665</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.0982</v>
+        <v>0.3094</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.31</v>
+        <v>-19.5739</v>
       </c>
       <c r="W11" t="n">
-        <v>2.0434</v>
+        <v>0.4450999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.3534</v>
+        <v>-20.0189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. MOLINA MATA</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.1628</v>
+        <v>-17.0611</v>
       </c>
       <c r="E12" t="n">
-        <v>-24.0117</v>
+        <v>-19.666</v>
       </c>
       <c r="F12" t="n">
-        <v>1.849</v>
+        <v>2.6049</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.4457</v>
+        <v>-6.0098</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.9079</v>
+        <v>7.0125</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.5376</v>
+        <v>-13.0225</v>
       </c>
       <c r="J12" t="n">
-        <v>2.206799999999999</v>
+        <v>-0.0138999999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4584</v>
+        <v>9.5466</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7488000000000006</v>
+        <v>-9.5603</v>
       </c>
       <c r="M12" t="n">
-        <v>-12.6524</v>
+        <v>-5.995699999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.366199999999999</v>
+        <v>-2.5339</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.2861</v>
+        <v>-3.4621</v>
       </c>
       <c r="P12" t="n">
-        <v>16.9846</v>
+        <v>-0.5793000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-19.6865</v>
+        <v>-20.6515</v>
       </c>
       <c r="R12" t="n">
-        <v>36.6713</v>
+        <v>20.0723</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.1279</v>
+        <v>-2.1624</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.9768</v>
+        <v>-1.0433</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.1514</v>
+        <v>-1.1189</v>
       </c>
       <c r="V12" t="n">
-        <v>-19.5739</v>
+        <v>-8.31</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4450999999999999</v>
+        <v>2.0434</v>
       </c>
       <c r="X12" t="n">
-        <v>-20.0189</v>
+        <v>-10.3534</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-46.6509</v>
+        <v>-45.88200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-43.5442</v>
+        <v>-40.4173</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1067</v>
+        <v>-5.4646</v>
       </c>
       <c r="G13" t="n">
         <v>-26.4549</v>
@@ -1468,13 +1468,13 @@
         <v>45.1639</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5087</v>
+        <v>-1.7396</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.4913</v>
+        <v>-3.3645</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9827</v>
+        <v>1.6249</v>
       </c>
       <c r="V13" t="n">
         <v>-21.1619</v>
@@ -1501,13 +1501,13 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-71.22789999999999</v>
+        <v>-58.1614</v>
       </c>
       <c r="E14" t="n">
-        <v>-75.04809999999999</v>
+        <v>-66.3165</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8209</v>
+        <v>8.1549</v>
       </c>
       <c r="G14" t="n">
         <v>-13.4201</v>
@@ -1546,13 +1546,13 @@
         <v>50.1823</v>
       </c>
       <c r="S14" t="n">
-        <v>-15.9152</v>
+        <v>-2.8492</v>
       </c>
       <c r="T14" t="n">
-        <v>-12.3688</v>
+        <v>-3.637</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5463</v>
+        <v>0.788</v>
       </c>
       <c r="V14" t="n">
         <v>-12.748</v>
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-110.7806</v>
+        <v>-84.7046</v>
       </c>
       <c r="E15" t="n">
-        <v>-110.4613</v>
+        <v>-94.40039999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3179000000000021</v>
+        <v>9.694899999999997</v>
       </c>
       <c r="G15" t="n">
         <v>37.84780000000001</v>
@@ -1594,7 +1594,7 @@
         <v>75.67519999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-37.8288</v>
+        <v>-37.82880000000001</v>
       </c>
       <c r="J15" t="n">
         <v>210.0489</v>
@@ -1603,7 +1603,7 @@
         <v>193.2901</v>
       </c>
       <c r="L15" t="n">
-        <v>16.75960000000001</v>
+        <v>16.7596</v>
       </c>
       <c r="M15" t="n">
         <v>-172.2001</v>
@@ -1618,19 +1618,19 @@
         <v>-32.8124</v>
       </c>
       <c r="Q15" t="n">
-        <v>-429.4407</v>
+        <v>-429.4406999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>396.6304000000001</v>
+        <v>396.6304</v>
       </c>
       <c r="S15" t="n">
-        <v>-26.3535</v>
+        <v>-0.2784999999999989</v>
       </c>
       <c r="T15" t="n">
-        <v>-23.5712</v>
+        <v>-7.5092</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.783099999999999</v>
+        <v>7.231300000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-89.46280000000002</v>
